--- a/Washing Machine Design Calculations.xlsx
+++ b/Washing Machine Design Calculations.xlsx
@@ -1,24 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/dcdf7eb514dfaeec/Projects/Microgravity-Press-Washing-Machine/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="75" documentId="13_ncr:1_{D766C26B-1EE4-490E-9437-84C4703C55A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{73C9E0BE-9C8D-449A-AA26-FEBA4B6F3122}"/>
+  <xr:revisionPtr revIDLastSave="98" documentId="13_ncr:1_{D766C26B-1EE4-490E-9437-84C4703C55A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7C91B7A4-938D-4B49-A253-C525D6E9D0F4}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="3" xr2:uid="{73A7591B-B5CA-4318-9343-9B3FDBEBCAB4}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{73A7591B-B5CA-4318-9343-9B3FDBEBCAB4}"/>
   </bookViews>
   <sheets>
     <sheet name="Design and Material Specs" sheetId="2" r:id="rId1"/>
     <sheet name="Motor Sizing Calcs" sheetId="1" r:id="rId2"/>
-    <sheet name="Piston Calcs" sheetId="11" r:id="rId3"/>
+    <sheet name="Piston Thrust Calcs" sheetId="11" r:id="rId3"/>
     <sheet name="Frame Calcs" sheetId="10" r:id="rId4"/>
     <sheet name="Screw Calculations" sheetId="9" r:id="rId5"/>
-    <sheet name="Piston Travel Calcs" sheetId="6" r:id="rId6"/>
+    <sheet name="Piston Travel &amp; Pressure Calcs" sheetId="6" r:id="rId6"/>
     <sheet name="Sources" sheetId="8" r:id="rId7"/>
     <sheet name="Equation Derivation" sheetId="3" r:id="rId8"/>
   </sheets>
@@ -31,15 +31,15 @@
     <definedName name="MachineHeight">'Design and Material Specs'!$D$12</definedName>
     <definedName name="MachineLength">'Design and Material Specs'!$D$14</definedName>
     <definedName name="MachineWidth">'Design and Material Specs'!$D$13</definedName>
-    <definedName name="MMH">'Piston Travel Calcs'!$B$3</definedName>
+    <definedName name="MMH">'Piston Travel &amp; Pressure Calcs'!$B$3</definedName>
     <definedName name="PistonSpeed">'Design and Material Specs'!$D$6</definedName>
-    <definedName name="PTIH">'Piston Travel Calcs'!$B$4</definedName>
+    <definedName name="PTIH">'Piston Travel &amp; Pressure Calcs'!$B$4</definedName>
     <definedName name="SS303FatigueStrength">'Design and Material Specs'!$N$4</definedName>
     <definedName name="SS303YieldStrength">'Design and Material Specs'!$O$4</definedName>
     <definedName name="SS303YoungsModulus">'Design and Material Specs'!$P$4</definedName>
     <definedName name="WashChamberDiameter">'Design and Material Specs'!$D$10</definedName>
-    <definedName name="WCID">'Piston Travel Calcs'!$B$2</definedName>
-    <definedName name="WPRT">'Piston Travel Calcs'!$B$1</definedName>
+    <definedName name="WCID">'Piston Travel &amp; Pressure Calcs'!$B$2</definedName>
+    <definedName name="WPRT">'Piston Travel &amp; Pressure Calcs'!$B$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -84,7 +84,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="658" uniqueCount="350">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="659" uniqueCount="350">
   <si>
     <t>Desired Force Application</t>
   </si>
@@ -509,9 +509,6 @@
     <t>RPM</t>
   </si>
   <si>
-    <t>Shaft Diamete</t>
-  </si>
-  <si>
     <t>Wash Chamber ID</t>
   </si>
   <si>
@@ -1134,6 +1131,9 @@
   </si>
   <si>
     <t>Width</t>
+  </si>
+  <si>
+    <t>Max Achievable Piston Pressure</t>
   </si>
 </sst>
 </file>
@@ -1163,7 +1163,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1209,6 +1209,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="2" tint="-0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1448,7 +1460,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1517,7 +1529,10 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1688,6 +1703,10 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2008,31 +2027,31 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8032333B-A9BC-44A5-9DD5-8238FAA8AC6A}">
   <dimension ref="C2:Q55"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="17" customWidth="1"/>
-    <col min="3" max="3" width="32.265625" customWidth="1"/>
-    <col min="12" max="12" width="8.1328125" customWidth="1"/>
-    <col min="13" max="13" width="19.1328125" customWidth="1"/>
-    <col min="14" max="14" width="18.73046875" customWidth="1"/>
-    <col min="15" max="15" width="18.3984375" customWidth="1"/>
-    <col min="16" max="16" width="14.73046875" customWidth="1"/>
+    <col min="3" max="3" width="32.21875" customWidth="1"/>
+    <col min="12" max="12" width="8.109375" customWidth="1"/>
+    <col min="13" max="13" width="19.109375" customWidth="1"/>
+    <col min="14" max="14" width="18.77734375" customWidth="1"/>
+    <col min="15" max="15" width="18.44140625" customWidth="1"/>
+    <col min="16" max="16" width="14.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="3:17" x14ac:dyDescent="0.45">
+    <row r="2" spans="3:17" x14ac:dyDescent="0.3">
       <c r="M2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="3:17" x14ac:dyDescent="0.45">
+    <row r="3" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C3" t="s">
         <v>3</v>
       </c>
       <c r="N3" t="s">
+        <v>203</v>
+      </c>
+      <c r="O3" t="s">
         <v>204</v>
-      </c>
-      <c r="O3" t="s">
-        <v>205</v>
       </c>
       <c r="P3" t="s">
         <v>22</v>
@@ -2041,7 +2060,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="3:17" x14ac:dyDescent="0.45">
+    <row r="4" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C4" t="s">
         <v>15</v>
       </c>
@@ -2052,7 +2071,7 @@
         <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="M4" t="s">
         <v>9</v>
@@ -2070,7 +2089,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="3:17" x14ac:dyDescent="0.45">
+    <row r="5" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C5" t="s">
         <v>0</v>
       </c>
@@ -2085,7 +2104,7 @@
         <v>2668.9332000000004</v>
       </c>
       <c r="M5" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="O5">
         <v>18100</v>
@@ -2094,10 +2113,10 @@
         <v>14500000</v>
       </c>
       <c r="Q5" s="3" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="6" spans="3:17" x14ac:dyDescent="0.45">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="6" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C6" t="s">
         <v>6</v>
       </c>
@@ -2108,7 +2127,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="3:17" x14ac:dyDescent="0.45">
+    <row r="7" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C7" t="s">
         <v>10</v>
       </c>
@@ -2119,17 +2138,17 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="3:17" x14ac:dyDescent="0.45">
+    <row r="8" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C8" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="9" spans="3:17" x14ac:dyDescent="0.45">
+    <row r="9" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C9" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="3:17" x14ac:dyDescent="0.45">
+    <row r="10" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C10" t="s">
         <v>67</v>
       </c>
@@ -2140,12 +2159,12 @@
         <v>71</v>
       </c>
     </row>
-    <row r="11" spans="3:17" x14ac:dyDescent="0.45">
+    <row r="11" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C11" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="12" spans="3:17" x14ac:dyDescent="0.45">
+    <row r="12" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C12" t="s">
         <v>69</v>
       </c>
@@ -2156,10 +2175,10 @@
         <v>71</v>
       </c>
       <c r="M12" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="13" spans="3:17" x14ac:dyDescent="0.45">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="13" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C13" t="s">
         <v>70</v>
       </c>
@@ -2176,7 +2195,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="3:17" x14ac:dyDescent="0.45">
+    <row r="14" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C14" t="s">
         <v>72</v>
       </c>
@@ -2196,9 +2215,9 @@
         <v>107</v>
       </c>
     </row>
-    <row r="15" spans="3:17" x14ac:dyDescent="0.45">
+    <row r="15" spans="3:17" x14ac:dyDescent="0.3">
       <c r="M15" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="N15">
         <v>0.19</v>
@@ -2210,20 +2229,20 @@
         <v>88</v>
       </c>
     </row>
-    <row r="16" spans="3:17" x14ac:dyDescent="0.45">
+    <row r="16" spans="3:17" x14ac:dyDescent="0.3">
       <c r="M16" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="N16">
         <v>4.4482220000000003</v>
       </c>
     </row>
-    <row r="22" spans="3:5" x14ac:dyDescent="0.45">
+    <row r="22" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C22" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="23" spans="3:5" x14ac:dyDescent="0.45">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="23" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C23" t="s">
         <v>69</v>
       </c>
@@ -2234,7 +2253,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="24" spans="3:5" x14ac:dyDescent="0.45">
+    <row r="24" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C24" t="s">
         <v>70</v>
       </c>
@@ -2246,7 +2265,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="25" spans="3:5" x14ac:dyDescent="0.45">
+    <row r="25" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C25" t="s">
         <v>72</v>
       </c>
@@ -2257,20 +2276,20 @@
         <v>71</v>
       </c>
     </row>
-    <row r="26" spans="3:5" x14ac:dyDescent="0.45">
+    <row r="26" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C26" t="s">
         <v>3</v>
       </c>
       <c r="D26" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="33" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="D33" s="3" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="33" spans="3:4" x14ac:dyDescent="0.45">
-      <c r="D33" s="3" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="48" spans="3:4" x14ac:dyDescent="0.45">
+    <row r="48" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C48" t="s">
         <v>43</v>
       </c>
@@ -2278,7 +2297,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="50" spans="3:13" x14ac:dyDescent="0.45">
+    <row r="50" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C50" t="s">
         <v>45</v>
       </c>
@@ -2301,7 +2320,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="51" spans="3:13" x14ac:dyDescent="0.45">
+    <row r="51" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C51" t="s">
         <v>50</v>
       </c>
@@ -2321,7 +2340,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="52" spans="3:13" x14ac:dyDescent="0.45">
+    <row r="52" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C52" t="s">
         <v>54</v>
       </c>
@@ -2341,7 +2360,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="53" spans="3:13" x14ac:dyDescent="0.45">
+    <row r="53" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C53" t="s">
         <v>58</v>
       </c>
@@ -2355,7 +2374,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="54" spans="3:13" x14ac:dyDescent="0.45">
+    <row r="54" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C54" t="s">
         <v>60</v>
       </c>
@@ -2375,7 +2394,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="55" spans="3:13" x14ac:dyDescent="0.45">
+    <row r="55" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C55" t="s">
         <v>64</v>
       </c>
@@ -2409,23 +2428,23 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F7F30C8-AEF8-4367-97CA-93B5B12A08F4}">
   <dimension ref="A1:AI56"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="40.265625" customWidth="1"/>
-    <col min="2" max="2" width="10.73046875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="41.1328125" customWidth="1"/>
-    <col min="6" max="6" width="35.86328125" customWidth="1"/>
-    <col min="8" max="8" width="5.73046875" customWidth="1"/>
-    <col min="10" max="10" width="12.265625" customWidth="1"/>
-    <col min="11" max="11" width="39.1328125" customWidth="1"/>
-    <col min="13" max="13" width="5.86328125" customWidth="1"/>
-    <col min="16" max="16" width="31.1328125" customWidth="1"/>
-    <col min="18" max="18" width="8.73046875" customWidth="1"/>
-    <col min="21" max="21" width="22.86328125" customWidth="1"/>
+    <col min="1" max="1" width="40.21875" customWidth="1"/>
+    <col min="2" max="2" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="41.109375" customWidth="1"/>
+    <col min="6" max="6" width="35.88671875" customWidth="1"/>
+    <col min="8" max="8" width="5.77734375" customWidth="1"/>
+    <col min="10" max="10" width="12.21875" customWidth="1"/>
+    <col min="11" max="11" width="39.109375" customWidth="1"/>
+    <col min="13" max="13" width="5.88671875" customWidth="1"/>
+    <col min="16" max="16" width="31.109375" customWidth="1"/>
+    <col min="18" max="18" width="8.77734375" customWidth="1"/>
+    <col min="21" max="21" width="22.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="2" spans="1:35" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A2" s="24" t="s">
         <v>121</v>
       </c>
@@ -2433,22 +2452,22 @@
       <c r="C2" s="25"/>
       <c r="D2" s="26"/>
       <c r="F2" s="38" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G2" s="39"/>
       <c r="H2" s="39"/>
       <c r="I2" s="40"/>
       <c r="K2" s="5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="L2" s="5"/>
       <c r="M2" s="5"/>
       <c r="N2" s="5"/>
       <c r="P2" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="3" spans="1:35" x14ac:dyDescent="0.45">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="3" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A3" s="10" t="s">
         <v>131</v>
       </c>
@@ -2489,7 +2508,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="4" spans="1:35" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="10" t="s">
         <v>1</v>
       </c>
@@ -2520,7 +2539,7 @@
       </c>
       <c r="N4" s="5"/>
       <c r="P4" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="Q4" s="1">
         <f>L5</f>
@@ -2530,7 +2549,7 @@
         <v>103</v>
       </c>
       <c r="S4" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="W4" s="46"/>
       <c r="X4" s="46"/>
@@ -2546,9 +2565,9 @@
       <c r="AH4" s="46"/>
       <c r="AI4" s="46"/>
     </row>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A5" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5"/>
@@ -2578,20 +2597,20 @@
       <c r="Y5" s="49"/>
       <c r="Z5" s="46"/>
       <c r="AA5" s="47" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="AB5" s="48"/>
       <c r="AC5" s="48"/>
       <c r="AD5" s="49"/>
       <c r="AE5" s="46"/>
       <c r="AF5" s="47" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="AG5" s="48"/>
       <c r="AH5" s="48"/>
       <c r="AI5" s="49"/>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A6" s="13"/>
       <c r="B6" s="5" t="s">
         <v>14</v>
@@ -2654,7 +2673,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A7" s="10" t="s">
         <v>85</v>
       </c>
@@ -2697,7 +2716,7 @@
       <c r="Y7" s="22"/>
       <c r="Z7" s="46"/>
       <c r="AA7" s="13" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="AB7" s="21">
         <v>0.5</v>
@@ -2708,7 +2727,7 @@
       <c r="AD7" s="22"/>
       <c r="AE7" s="46"/>
       <c r="AF7" s="13" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AG7" s="21">
         <f>W7</f>
@@ -2719,7 +2738,7 @@
       </c>
       <c r="AI7" s="22"/>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A8" s="10" t="s">
         <v>83</v>
       </c>
@@ -2760,11 +2779,11 @@
         <v>71</v>
       </c>
       <c r="Y8" s="22" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="Z8" s="46"/>
       <c r="AA8" s="13" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="AB8" s="21">
         <v>2</v>
@@ -2775,7 +2794,7 @@
       <c r="AD8" s="22"/>
       <c r="AE8" s="46"/>
       <c r="AF8" s="13" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="AG8" s="21">
         <f>AB9</f>
@@ -2784,7 +2803,7 @@
       <c r="AH8" s="21"/>
       <c r="AI8" s="22"/>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A9" s="10" t="s">
         <v>86</v>
       </c>
@@ -2827,7 +2846,7 @@
       <c r="Y9" s="22"/>
       <c r="Z9" s="46"/>
       <c r="AA9" s="13" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="AB9" s="21">
         <f>AB7*AB8</f>
@@ -2839,7 +2858,7 @@
       <c r="AD9" s="22"/>
       <c r="AE9" s="46"/>
       <c r="AF9" s="13" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AG9" s="21">
         <f>SS303FatigueStrength</f>
@@ -2850,7 +2869,7 @@
       </c>
       <c r="AI9" s="22"/>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A10" s="10" t="s">
         <v>89</v>
       </c>
@@ -2889,12 +2908,12 @@
         <v>1487.5</v>
       </c>
       <c r="X10" s="21" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Y10" s="22"/>
       <c r="Z10" s="46"/>
       <c r="AA10" s="13" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="AB10" s="21">
         <f>SQRT((6*W13)/AB9)</f>
@@ -2914,7 +2933,7 @@
       <c r="AH10" s="21"/>
       <c r="AI10" s="22"/>
     </row>
-    <row r="11" spans="1:35" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="11" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="10" t="s">
         <v>10</v>
       </c>
@@ -2962,7 +2981,7 @@
       <c r="AD11" s="52"/>
       <c r="AE11" s="46"/>
       <c r="AF11" s="13" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="AG11" s="21">
         <f>AG7*AG10*FS/(AG9*AG8)</f>
@@ -2971,7 +2990,7 @@
       <c r="AH11" s="21"/>
       <c r="AI11" s="22"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A12" s="10" t="s">
         <v>90</v>
       </c>
@@ -3008,7 +3027,7 @@
         <v>34800</v>
       </c>
       <c r="X12" s="21" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="Y12" s="22"/>
       <c r="Z12" s="46"/>
@@ -3018,7 +3037,7 @@
       <c r="AD12" s="46"/>
       <c r="AE12" s="46"/>
       <c r="AF12" s="13" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="AG12" s="21">
         <f>2*SQRT((AG7*FS/AB8)/AG9)</f>
@@ -3027,7 +3046,7 @@
       <c r="AH12" s="21"/>
       <c r="AI12" s="22"/>
     </row>
-    <row r="13" spans="1:35" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="13" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="10" t="s">
         <v>93</v>
       </c>
@@ -3056,7 +3075,7 @@
         <v>8.5488505747126436E-2</v>
       </c>
       <c r="X13" s="51" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="Y13" s="52"/>
       <c r="Z13" s="46"/>
@@ -3066,7 +3085,7 @@
       <c r="AD13" s="46"/>
       <c r="AE13" s="46"/>
       <c r="AF13" s="50" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AG13" s="51">
         <f>3/8</f>
@@ -3075,7 +3094,7 @@
       <c r="AH13" s="51"/>
       <c r="AI13" s="52"/>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A14" s="13"/>
       <c r="B14" s="21"/>
       <c r="C14" s="21"/>
@@ -3105,7 +3124,7 @@
       <c r="AH14" s="46"/>
       <c r="AI14" s="46"/>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A15" s="14" t="s">
         <v>94</v>
       </c>
@@ -3139,7 +3158,7 @@
       <c r="AH15" s="46"/>
       <c r="AI15" s="46"/>
     </row>
-    <row r="16" spans="1:35" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="16" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="14" t="s">
         <v>91</v>
       </c>
@@ -3166,7 +3185,7 @@
       <c r="Y16" s="46"/>
       <c r="Z16" s="46"/>
       <c r="AA16" s="46" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="AB16" s="46"/>
       <c r="AC16" s="46"/>
@@ -3177,7 +3196,7 @@
       <c r="AH16" s="46"/>
       <c r="AI16" s="46"/>
     </row>
-    <row r="17" spans="1:35" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="17" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="14" t="s">
         <v>96</v>
       </c>
@@ -3203,7 +3222,7 @@
       <c r="Y17" s="49"/>
       <c r="Z17" s="46"/>
       <c r="AA17" s="47" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="AB17" s="48"/>
       <c r="AC17" s="48"/>
@@ -3214,7 +3233,7 @@
       <c r="AH17" s="46"/>
       <c r="AI17" s="46"/>
     </row>
-    <row r="18" spans="1:35" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="18" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="18" t="s">
         <v>105</v>
       </c>
@@ -3250,7 +3269,7 @@
       <c r="AH18" s="46"/>
       <c r="AI18" s="46"/>
     </row>
-    <row r="19" spans="1:35" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:35" x14ac:dyDescent="0.3">
       <c r="W19" s="21">
         <f>0.125</f>
         <v>0.125</v>
@@ -3261,7 +3280,7 @@
       <c r="Y19" s="22"/>
       <c r="Z19" s="46"/>
       <c r="AA19" s="13" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="AB19" s="21">
         <f>0.125</f>
@@ -3277,7 +3296,7 @@
       <c r="AH19" s="46"/>
       <c r="AI19" s="46"/>
     </row>
-    <row r="20" spans="1:35" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:35" x14ac:dyDescent="0.3">
       <c r="W20" s="21">
         <f>SS303FatigueStrength</f>
         <v>34800</v>
@@ -3288,7 +3307,7 @@
       <c r="Y20" s="22"/>
       <c r="Z20" s="46"/>
       <c r="AA20" s="13" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AB20" s="21">
         <f>SS303FatigueStrength</f>
@@ -3304,7 +3323,7 @@
       <c r="AH20" s="46"/>
       <c r="AI20" s="46"/>
     </row>
-    <row r="21" spans="1:35" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:35" x14ac:dyDescent="0.3">
       <c r="F21" t="s">
         <v>119</v>
       </c>
@@ -3331,9 +3350,9 @@
       <c r="AH21" s="46"/>
       <c r="AI21" s="46"/>
     </row>
-    <row r="22" spans="1:35" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F22" t="s">
         <v>125</v>
@@ -3351,7 +3370,7 @@
       <c r="Y22" s="22"/>
       <c r="Z22" s="46"/>
       <c r="AA22" s="13" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AB22" s="21">
         <f>AB21*AppliedForceNormal*0.5/(2*AB19*AB20)</f>
@@ -3367,7 +3386,7 @@
       <c r="AH22" s="46"/>
       <c r="AI22" s="46"/>
     </row>
-    <row r="23" spans="1:35" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="23" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>136</v>
       </c>
@@ -3380,7 +3399,7 @@
       <c r="Y23" s="52"/>
       <c r="Z23" s="46"/>
       <c r="AA23" s="50" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="AB23" s="51">
         <v>0.25</v>
@@ -3395,13 +3414,13 @@
       <c r="AH23" s="46"/>
       <c r="AI23" s="46"/>
     </row>
-    <row r="24" spans="1:35" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:35" x14ac:dyDescent="0.3">
       <c r="W24" s="46"/>
       <c r="X24" s="46"/>
       <c r="Y24" s="46"/>
       <c r="Z24" s="46"/>
       <c r="AA24" s="53" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="AB24" s="46">
         <f>W23+(2*AB23)</f>
@@ -3415,15 +3434,15 @@
       <c r="AH24" s="46"/>
       <c r="AI24" s="46"/>
     </row>
-    <row r="27" spans="1:35" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="27" spans="1:35" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F27" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="28" spans="1:35" x14ac:dyDescent="0.45">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="28" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A28" s="31"/>
       <c r="B28" s="32" t="s">
         <v>14</v>
@@ -3445,9 +3464,9 @@
         <v>129</v>
       </c>
     </row>
-    <row r="29" spans="1:35" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A29" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B29" s="27">
         <f>ROUND(L9*B8,1)</f>
@@ -3457,19 +3476,19 @@
         <v>102</v>
       </c>
       <c r="D29" s="11" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="F29" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="G29">
         <f>B34/(B30/12)</f>
         <v>30.42</v>
       </c>
     </row>
-    <row r="30" spans="1:35" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A30" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B30" s="41">
         <f>2</f>
@@ -3479,15 +3498,15 @@
         <v>71</v>
       </c>
       <c r="D30" s="11" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F30" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="31" spans="1:35" x14ac:dyDescent="0.45">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="31" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A31" s="10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B31" s="5">
         <f>B29/(B30/12)</f>
@@ -3498,12 +3517,12 @@
       </c>
       <c r="D31" s="11"/>
       <c r="F31" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="32" spans="1:35" x14ac:dyDescent="0.45">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="32" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A32" s="10" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B32" s="5">
         <v>1.25</v>
@@ -3513,9 +3532,9 @@
       </c>
       <c r="D32" s="11"/>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" s="10" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B33" s="42">
         <v>0.96</v>
@@ -3523,9 +3542,9 @@
       <c r="C33" s="5"/>
       <c r="D33" s="11"/>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" s="10" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B34" s="27">
         <f>B29*(B32/B30)*(1-B33+1)</f>
@@ -3536,12 +3555,12 @@
       </c>
       <c r="D34" s="43"/>
       <c r="I34" s="3" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.45">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" s="10" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B35" s="27">
         <f>B34*16*12</f>
@@ -3552,9 +3571,9 @@
       </c>
       <c r="D35" s="11"/>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" s="10" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B36" s="27">
         <f>B34*0.4535*30.48</f>
@@ -3565,7 +3584,7 @@
       </c>
       <c r="D36" s="11"/>
     </row>
-    <row r="37" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="37" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A37" s="23" t="s">
         <v>139</v>
       </c>
@@ -3576,12 +3595,12 @@
       <c r="C37" s="34"/>
       <c r="D37" s="30"/>
     </row>
-    <row r="40" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="40" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="F40" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>124</v>
       </c>
@@ -3596,7 +3615,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" s="31"/>
       <c r="B42" s="32" t="s">
         <v>14</v>
@@ -3608,7 +3627,7 @@
         <v>129</v>
       </c>
       <c r="F42" s="10" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G42" s="6">
         <v>19</v>
@@ -3618,9 +3637,9 @@
       </c>
       <c r="I42" s="11"/>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" s="10" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B43" s="27">
         <f>B34</f>
@@ -3631,7 +3650,7 @@
       </c>
       <c r="D43" s="11"/>
       <c r="F43" s="10" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="G43" s="6">
         <v>1</v>
@@ -3641,9 +3660,9 @@
       </c>
       <c r="I43" s="11"/>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44" s="10" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B44" s="27">
         <f>B43*16*12</f>
@@ -3654,7 +3673,7 @@
       </c>
       <c r="D44" s="11"/>
       <c r="F44" s="10" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="G44" s="8">
         <f>B37</f>
@@ -3663,9 +3682,9 @@
       <c r="H44" s="5"/>
       <c r="I44" s="11"/>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" s="10" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B45" s="27">
         <f>B43*0.4535*30.48</f>
@@ -3676,31 +3695,31 @@
       </c>
       <c r="D45" s="11"/>
       <c r="F45" s="10" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="G45" s="8">
         <f>G15</f>
         <v>10</v>
       </c>
       <c r="H45" s="5" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="I45" s="11"/>
     </row>
-    <row r="46" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="46" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A46" s="23" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B46" s="34">
         <f>B43*1.3558179483</f>
         <v>6.873996997881</v>
       </c>
       <c r="C46" s="34" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D46" s="30"/>
       <c r="F46" s="10" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="G46" s="7">
         <f>G42/(G43*G44)</f>
@@ -3711,86 +3730,86 @@
       </c>
       <c r="I46" s="11"/>
     </row>
-    <row r="47" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="47" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="F47" s="23" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="G47" s="34">
         <f>G46/G45</f>
         <v>1.1875</v>
       </c>
       <c r="H47" s="34" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="I47" s="30"/>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A49" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="D50">
         <v>50</v>
       </c>
       <c r="E50" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.45">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="D51">
         <f>2*PI()*D50/60</f>
         <v>5.2359877559829888</v>
       </c>
       <c r="E51" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="F51" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.45">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="D52">
         <f>B46</f>
         <v>6.873996997881</v>
       </c>
       <c r="E52" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.45">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="D53">
         <f>D51*D52</f>
         <v>35.992164115568741</v>
       </c>
       <c r="E53" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="F53">
         <f>0.105*90*B46</f>
         <v>64.959271629975447</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="D55">
         <v>24</v>
       </c>
       <c r="E55" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.45">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="D56">
         <f>D53/D55</f>
         <v>1.4996735048153642</v>
       </c>
       <c r="E56" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F56">
         <f>6000*0.224808943</f>
@@ -3810,21 +3829,21 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35650138-A39B-40B7-A1C0-41B1A4232402}">
   <dimension ref="A1:X50"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="39.3984375" customWidth="1"/>
-    <col min="6" max="6" width="34.73046875" customWidth="1"/>
-    <col min="11" max="11" width="25.73046875" customWidth="1"/>
+    <col min="1" max="1" width="39.44140625" customWidth="1"/>
+    <col min="6" max="6" width="34.77734375" customWidth="1"/>
+    <col min="11" max="11" width="25.77734375" customWidth="1"/>
     <col min="16" max="16" width="17" customWidth="1"/>
-    <col min="21" max="21" width="19.73046875" customWidth="1"/>
+    <col min="21" max="21" width="19.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.45">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" s="31" t="s">
         <v>8</v>
       </c>
@@ -3832,19 +3851,19 @@
       <c r="C2" s="32"/>
       <c r="D2" s="33"/>
       <c r="F2" s="5" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G2" s="5"/>
       <c r="H2" s="5"/>
       <c r="I2" s="5"/>
       <c r="K2" s="31" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L2" s="32"/>
       <c r="M2" s="32"/>
       <c r="N2" s="33"/>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" s="10"/>
       <c r="B3" s="5" t="s">
         <v>14</v>
@@ -3876,7 +3895,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="10" t="s">
         <v>18</v>
       </c>
@@ -3888,7 +3907,7 @@
       </c>
       <c r="D4" s="11"/>
       <c r="F4" s="5" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="G4" s="5">
         <f>B12</f>
@@ -3899,7 +3918,7 @@
       </c>
       <c r="I4" s="5"/>
       <c r="K4" s="10" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="L4" s="5">
         <v>0.75</v>
@@ -3909,7 +3928,7 @@
       </c>
       <c r="N4" s="11"/>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" s="10" t="s">
         <v>19</v>
       </c>
@@ -3920,7 +3939,7 @@
       <c r="C5" s="5"/>
       <c r="D5" s="11"/>
       <c r="F5" s="5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G5" s="5">
         <f>SS303FatigueStrength</f>
@@ -3931,18 +3950,18 @@
       </c>
       <c r="I5" s="5"/>
       <c r="K5" s="10" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="L5" s="5">
         <f>(L4^2)*PI()</f>
         <v>1.7671458676442586</v>
       </c>
       <c r="M5" s="5" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="N5" s="11"/>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" s="10" t="s">
         <v>20</v>
       </c>
@@ -3972,7 +3991,7 @@
       </c>
       <c r="N6" s="11"/>
     </row>
-    <row r="7" spans="1:14" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
         <v>21</v>
       </c>
@@ -3983,7 +4002,7 @@
       <c r="C7" s="5"/>
       <c r="D7" s="11"/>
       <c r="F7" s="5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="G7" s="5">
         <f>AppliedForceNormal*G6/(G5*G4)</f>
@@ -3992,7 +4011,7 @@
       <c r="H7" s="5"/>
       <c r="I7" s="5"/>
       <c r="K7" s="23" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="L7" s="34">
         <f>L6/L5</f>
@@ -4003,7 +4022,7 @@
       </c>
       <c r="N7" s="30"/>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" s="10" t="s">
         <v>23</v>
       </c>
@@ -4014,7 +4033,7 @@
       <c r="C8" s="5"/>
       <c r="D8" s="11"/>
       <c r="F8" s="5" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G8" s="5">
         <f>3/8</f>
@@ -4023,7 +4042,7 @@
       <c r="H8" s="5"/>
       <c r="I8" s="5"/>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" s="10" t="s">
         <v>10</v>
       </c>
@@ -4034,7 +4053,7 @@
       <c r="C9" s="5"/>
       <c r="D9" s="11"/>
       <c r="F9" s="5" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="G9" s="5">
         <f>(((G4/2)^2)*PI())-(G4*G8)</f>
@@ -4043,7 +4062,7 @@
       <c r="H9" s="5"/>
       <c r="I9" s="5"/>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" s="10" t="s">
         <v>73</v>
       </c>
@@ -4054,7 +4073,7 @@
       <c r="C10" s="5"/>
       <c r="D10" s="11"/>
       <c r="F10" s="5" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G10" s="5">
         <f>AppliedForceNormal/G9</f>
@@ -4065,7 +4084,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" s="10" t="s">
         <v>74</v>
       </c>
@@ -4076,7 +4095,7 @@
       <c r="C11" s="5"/>
       <c r="D11" s="11"/>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" s="10" t="s">
         <v>75</v>
       </c>
@@ -4088,13 +4107,13 @@
       </c>
       <c r="D12" s="11"/>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" s="10"/>
       <c r="B13" s="5"/>
       <c r="C13" s="5"/>
       <c r="D13" s="11"/>
       <c r="F13" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G13" s="5" t="s">
         <v>14</v>
@@ -4106,9 +4125,9 @@
         <v>129</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" s="10" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B14" s="5">
         <f>((PI()^2)*B6)/((B8/(B12/2))^2)</f>
@@ -4118,10 +4137,10 @@
         <v>13</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G14" s="5">
         <f>WashChamberDiameter</f>
@@ -4130,9 +4149,9 @@
       <c r="H14" s="5"/>
       <c r="I14" s="5"/>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" s="35" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B15" s="36">
         <f>B14*(((B12/2)^2)*PI())</f>
@@ -4143,7 +4162,7 @@
       </c>
       <c r="D15" s="37"/>
       <c r="F15" s="5" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G15" s="5">
         <v>0.25</v>
@@ -4151,7 +4170,7 @@
       <c r="H15" s="5"/>
       <c r="I15" s="5"/>
     </row>
-    <row r="16" spans="1:14" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="16" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="23" t="s">
         <v>87</v>
       </c>
@@ -4159,7 +4178,7 @@
       <c r="C16" s="34"/>
       <c r="D16" s="30"/>
       <c r="F16" s="5" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G16" s="5">
         <f>(G14-(2*G15))/G8</f>
@@ -4168,9 +4187,9 @@
       <c r="H16" s="5"/>
       <c r="I16" s="5"/>
     </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:24" x14ac:dyDescent="0.3">
       <c r="F17" s="5" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G17" s="5">
         <v>10</v>
@@ -4178,44 +4197,44 @@
       <c r="H17" s="5"/>
       <c r="I17" s="5"/>
     </row>
-    <row r="21" spans="1:24" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="21" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="22" spans="1:24" x14ac:dyDescent="0.45">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="22" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A22" s="31" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B22" s="32"/>
       <c r="C22" s="32"/>
       <c r="D22" s="33"/>
       <c r="F22" s="31" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G22" s="32"/>
       <c r="H22" s="32"/>
       <c r="I22" s="33"/>
       <c r="K22" s="5" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="L22" s="5"/>
       <c r="M22" s="5"/>
       <c r="N22" s="5"/>
       <c r="P22" s="5" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="Q22" s="5"/>
       <c r="R22" s="5"/>
       <c r="S22" s="5"/>
       <c r="U22" s="31" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="V22" s="32"/>
       <c r="W22" s="32"/>
       <c r="X22" s="33"/>
     </row>
-    <row r="23" spans="1:24" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A23" s="10"/>
       <c r="B23" s="5" t="s">
         <v>14</v>
@@ -4267,7 +4286,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="24" spans="1:24" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A24" s="10" t="s">
         <v>80</v>
       </c>
@@ -4276,7 +4295,7 @@
         <v>12.566370614359172</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D24" s="11"/>
       <c r="F24" s="10" t="s">
@@ -4286,7 +4305,7 @@
       <c r="H24" s="5"/>
       <c r="I24" s="11"/>
       <c r="K24" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="L24" s="5">
         <f>G34</f>
@@ -4297,7 +4316,7 @@
       </c>
       <c r="N24" s="5"/>
       <c r="P24" s="5" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="Q24" s="5">
         <f>G25</f>
@@ -4306,7 +4325,7 @@
       <c r="R24" s="5"/>
       <c r="S24" s="5"/>
       <c r="U24" s="10" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="V24" s="5">
         <f>3/8</f>
@@ -4317,7 +4336,7 @@
       </c>
       <c r="X24" s="11"/>
     </row>
-    <row r="25" spans="1:24" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A25" s="10" t="s">
         <v>78</v>
       </c>
@@ -4338,7 +4357,7 @@
       <c r="H25" s="5"/>
       <c r="I25" s="11"/>
       <c r="K25" s="5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="L25" s="5">
         <f>SS303FatigueStrength</f>
@@ -4349,24 +4368,24 @@
       </c>
       <c r="N25" s="5"/>
       <c r="P25" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q25" s="5"/>
       <c r="R25" s="5"/>
       <c r="S25" s="5"/>
       <c r="U25" s="10" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="V25" s="5">
         <f>(V24^2)*PI()</f>
         <v>0.44178646691106466</v>
       </c>
       <c r="W25" s="5" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="X25" s="11"/>
     </row>
-    <row r="26" spans="1:24" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A26" s="10" t="s">
         <v>79</v>
       </c>
@@ -4375,7 +4394,7 @@
         <v>11.965050145508002</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D26" s="11"/>
       <c r="F26" s="10" t="s">
@@ -4395,7 +4414,7 @@
       <c r="M26" s="5"/>
       <c r="N26" s="5"/>
       <c r="P26" s="5" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="Q26" s="5">
         <f>G34</f>
@@ -4415,7 +4434,7 @@
       </c>
       <c r="X26" s="11"/>
     </row>
-    <row r="27" spans="1:24" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="27" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="23" t="s">
         <v>77</v>
       </c>
@@ -4437,7 +4456,7 @@
       <c r="H27" s="5"/>
       <c r="I27" s="11"/>
       <c r="K27" s="5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L27" s="5">
         <f>(G29*L26/G25)/(L25*L24)</f>
@@ -4450,7 +4469,7 @@
       <c r="R27" s="5"/>
       <c r="S27" s="5"/>
       <c r="U27" s="23" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="V27" s="34">
         <f>V26/V25</f>
@@ -4461,7 +4480,7 @@
       </c>
       <c r="X27" s="30"/>
     </row>
-    <row r="28" spans="1:24" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:24" x14ac:dyDescent="0.3">
       <c r="F28" s="10" t="s">
         <v>20</v>
       </c>
@@ -4472,7 +4491,7 @@
       <c r="H28" s="5"/>
       <c r="I28" s="11"/>
       <c r="K28" s="5" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="L28" s="27">
         <f>(0.25+0.125)/2</f>
@@ -4485,7 +4504,7 @@
       <c r="R28" s="5"/>
       <c r="S28" s="5"/>
     </row>
-    <row r="29" spans="1:24" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:24" x14ac:dyDescent="0.3">
       <c r="F29" s="10" t="s">
         <v>21</v>
       </c>
@@ -4498,7 +4517,7 @@
       </c>
       <c r="I29" s="11"/>
       <c r="K29" s="5" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="L29" s="5">
         <f>(((L24/2)^2)*PI())-(L24*L28)</f>
@@ -4511,7 +4530,7 @@
       <c r="R29" s="5"/>
       <c r="S29" s="5"/>
     </row>
-    <row r="30" spans="1:24" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:24" x14ac:dyDescent="0.3">
       <c r="F30" s="10" t="s">
         <v>23</v>
       </c>
@@ -4524,7 +4543,7 @@
       </c>
       <c r="I30" s="11"/>
       <c r="K30" s="5" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="L30" s="5">
         <f>(G29/G25)/L29</f>
@@ -4539,7 +4558,7 @@
       <c r="R30" s="5"/>
       <c r="S30" s="5"/>
     </row>
-    <row r="31" spans="1:24" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:24" x14ac:dyDescent="0.3">
       <c r="F31" s="10" t="s">
         <v>10</v>
       </c>
@@ -4551,7 +4570,7 @@
       </c>
       <c r="I31" s="11"/>
     </row>
-    <row r="32" spans="1:24" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:24" x14ac:dyDescent="0.3">
       <c r="F32" s="10" t="s">
         <v>73</v>
       </c>
@@ -4560,11 +4579,11 @@
         <v>0.15686758558106753</v>
       </c>
       <c r="H32" s="5" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I32" s="11"/>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="F33" s="10" t="s">
         <v>74</v>
       </c>
@@ -4577,7 +4596,7 @@
       </c>
       <c r="I33" s="11"/>
       <c r="K33" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="L33" s="5" t="s">
         <v>14</v>
@@ -4589,7 +4608,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="F34" s="10" t="s">
         <v>75</v>
       </c>
@@ -4601,7 +4620,7 @@
       </c>
       <c r="I34" s="11"/>
       <c r="K34" s="5" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="L34" s="5">
         <f>1.29*2</f>
@@ -4609,16 +4628,16 @@
       </c>
       <c r="M34" s="5"/>
       <c r="N34" s="5" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.45">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="F35" s="10"/>
       <c r="G35" s="5"/>
       <c r="H35" s="5"/>
       <c r="I35" s="11"/>
       <c r="K35" s="5" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="L35" s="5">
         <v>0.25</v>
@@ -4626,9 +4645,9 @@
       <c r="M35" s="5"/>
       <c r="N35" s="5"/>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="F36" s="10" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G36" s="5">
         <f>((PI()^2)*G28)/((G30/(G34/2))^2)</f>
@@ -4638,10 +4657,10 @@
         <v>13</v>
       </c>
       <c r="I36" s="11" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="K36" s="5" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="L36" s="5">
         <f>(L34-(2*L35))/L28</f>
@@ -4650,9 +4669,9 @@
       <c r="M36" s="5"/>
       <c r="N36" s="5"/>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="F37" s="10" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G37" s="5">
         <f>G36*(((G34/2)^2)*PI())</f>
@@ -4663,17 +4682,17 @@
       </c>
       <c r="I37" s="11"/>
       <c r="K37" s="5" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="L37" s="5">
         <v>10</v>
       </c>
       <c r="M37" s="5"/>
       <c r="N37" s="5" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="38" spans="1:14" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="F38" s="23" t="s">
         <v>87</v>
       </c>
@@ -4681,32 +4700,32 @@
       <c r="H38" s="34"/>
       <c r="I38" s="30"/>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.45">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A42" s="5" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B42" s="5"/>
       <c r="C42" s="5"/>
       <c r="D42" s="5"/>
       <c r="F42" s="5" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="G42" s="5"/>
       <c r="H42" s="5"/>
       <c r="I42" s="5"/>
       <c r="K42" s="5" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="L42" s="5"/>
       <c r="M42" s="5"/>
       <c r="N42" s="5"/>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A43" s="5"/>
       <c r="B43" s="5" t="s">
         <v>14</v>
@@ -4738,9 +4757,9 @@
         <v>129</v>
       </c>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A44" s="5" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B44" s="5">
         <f>AppliedForceNormal</f>
@@ -4751,7 +4770,7 @@
       </c>
       <c r="D44" s="5"/>
       <c r="F44" s="5" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="G44" s="5">
         <v>0.25</v>
@@ -4761,7 +4780,7 @@
       </c>
       <c r="I44" s="5"/>
       <c r="K44" s="5" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="L44" s="5">
         <v>1</v>
@@ -4771,9 +4790,9 @@
       </c>
       <c r="N44" s="5"/>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A45" s="5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B45" s="5">
         <f>3.725*2</f>
@@ -4783,10 +4802,10 @@
         <v>71</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F45" s="5" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="G45" s="5">
         <v>2</v>
@@ -4796,7 +4815,7 @@
       </c>
       <c r="I45" s="5"/>
       <c r="K45" s="5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="L45" s="5">
         <f>SS303FatigueStrength</f>
@@ -4807,9 +4826,9 @@
       </c>
       <c r="N45" s="5"/>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A46" s="5" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B46" s="5">
         <f>B44/2</f>
@@ -4820,7 +4839,7 @@
       </c>
       <c r="D46" s="5"/>
       <c r="F46" s="5" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G46" s="5">
         <f>G44*G45</f>
@@ -4839,20 +4858,20 @@
       <c r="M46" s="5"/>
       <c r="N46" s="5"/>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A47" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B47" s="5">
         <f>B46*B45/2</f>
         <v>1117.5</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D47" s="5"/>
       <c r="F47" s="5" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="G47" s="5">
         <f>SQRT((6*B50)/G46)</f>
@@ -4863,7 +4882,7 @@
       </c>
       <c r="I47" s="5"/>
       <c r="K47" s="5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L47" s="5">
         <f>AppliedForceNormal*L46/(L45*L44)</f>
@@ -4872,7 +4891,7 @@
       <c r="M47" s="5"/>
       <c r="N47" s="5"/>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A48" s="5" t="s">
         <v>10</v>
       </c>
@@ -4886,7 +4905,7 @@
       <c r="H48" s="5"/>
       <c r="I48" s="5"/>
       <c r="K48" s="5" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="L48" s="5">
         <v>0.25</v>
@@ -4894,9 +4913,9 @@
       <c r="M48" s="5"/>
       <c r="N48" s="5"/>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A49" s="5" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B49" s="5">
         <f>SS303FatigueStrength</f>
@@ -4905,7 +4924,7 @@
       <c r="C49" s="5"/>
       <c r="D49" s="5"/>
       <c r="K49" s="5" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="L49" s="5">
         <f>(((L44/2)^2)*PI())-(L44*L48)</f>
@@ -4914,9 +4933,9 @@
       <c r="M49" s="5"/>
       <c r="N49" s="5"/>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A50" s="5" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B50" s="5">
         <f>B47*B48/B49</f>
@@ -4925,7 +4944,7 @@
       <c r="C50" s="5"/>
       <c r="D50" s="5"/>
       <c r="K50" s="5" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="L50" s="5">
         <f>AppliedForceNormal/L49</f>
@@ -4944,24 +4963,24 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58B192C6-AACC-4DBA-B547-B2E0428B8816}">
   <dimension ref="A2:H33"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="21.796875" customWidth="1"/>
-    <col min="2" max="2" width="26.59765625" customWidth="1"/>
+    <col min="1" max="1" width="21.77734375" customWidth="1"/>
+    <col min="2" max="2" width="26.5546875" customWidth="1"/>
     <col min="7" max="7" width="26" customWidth="1"/>
-    <col min="12" max="12" width="32.73046875" customWidth="1"/>
+    <col min="12" max="12" width="32.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:5" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B3" s="31"/>
       <c r="C3" s="32"/>
       <c r="D3" s="32"/>
       <c r="E3" s="33"/>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B4" s="10" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C4" s="5">
         <v>0.125</v>
@@ -4971,9 +4990,9 @@
       </c>
       <c r="E4" s="11"/>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B5" s="10" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -4983,22 +5002,22 @@
       </c>
       <c r="E5" s="11"/>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B6" s="10" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C6">
         <f>C5*C4</f>
         <v>0.125</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E6" s="11"/>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B7" s="10" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C7">
         <f>C18/C6</f>
@@ -5009,7 +5028,7 @@
       </c>
       <c r="E7" s="11"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B8" s="10" t="s">
         <v>10</v>
       </c>
@@ -5022,12 +5041,12 @@
       </c>
       <c r="E8" s="11"/>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C9" s="5">
         <v>0.25</v>
@@ -5035,9 +5054,9 @@
       <c r="D9" s="5"/>
       <c r="E9" s="11"/>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B10" s="10" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C10" s="5">
         <f>C4*C9</f>
@@ -5046,9 +5065,9 @@
       <c r="D10" s="5"/>
       <c r="E10" s="11"/>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B11" s="54" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C11">
         <f>C18/C10</f>
@@ -5057,7 +5076,7 @@
       <c r="D11" s="5"/>
       <c r="E11" s="11"/>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B12" s="54" t="s">
         <v>10</v>
       </c>
@@ -5068,12 +5087,12 @@
       <c r="D12" s="5"/>
       <c r="E12" s="11"/>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
+        <v>344</v>
+      </c>
+      <c r="B13" s="10" t="s">
         <v>345</v>
-      </c>
-      <c r="B13" s="10" t="s">
-        <v>346</v>
       </c>
       <c r="C13">
         <f>(C9/2)^2*PI()</f>
@@ -5082,14 +5101,14 @@
       <c r="D13" s="5"/>
       <c r="E13" s="11"/>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B14" s="10"/>
       <c r="D14" s="5"/>
       <c r="E14" s="11"/>
     </row>
-    <row r="15" spans="1:5" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="15" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B15" s="23" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C15">
         <f>C6-C10</f>
@@ -5098,38 +5117,38 @@
       <c r="D15" s="34"/>
       <c r="E15" s="30"/>
     </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.45">
+    <row r="17" spans="2:8" x14ac:dyDescent="0.3">
       <c r="C17" s="5">
         <f>SS303FatigueStrength</f>
         <v>34800</v>
       </c>
     </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.45">
+    <row r="18" spans="2:8" x14ac:dyDescent="0.3">
       <c r="C18" s="5">
         <f>AppliedForceNormal</f>
         <v>600</v>
       </c>
     </row>
-    <row r="23" spans="2:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="23" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B23" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.45">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="24" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B24" s="31" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C24" s="32"/>
       <c r="D24" s="32"/>
       <c r="E24" s="33"/>
       <c r="G24" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H24">
         <v>0.25</v>
       </c>
     </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.45">
+    <row r="25" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B25" s="10"/>
       <c r="C25" s="5" t="s">
         <v>14</v>
@@ -5141,15 +5160,15 @@
         <v>129</v>
       </c>
       <c r="G25" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H25">
         <v>1.75</v>
       </c>
     </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.45">
+    <row r="26" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B26" s="10" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C26" s="5">
         <v>200</v>
@@ -5158,19 +5177,19 @@
         <v>103</v>
       </c>
       <c r="E26" s="11" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="G26" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H26">
         <f>(H24*H25^2)/6</f>
         <v>0.12760416666666666</v>
       </c>
     </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.45">
+    <row r="27" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B27" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C27" s="5">
         <f>AppliedForceNormal+C26</f>
@@ -5181,9 +5200,9 @@
       </c>
       <c r="E27" s="11"/>
     </row>
-    <row r="28" spans="2:8" x14ac:dyDescent="0.45">
+    <row r="28" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B28" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C28" s="5">
         <f>MachineWidth-0.25</f>
@@ -5193,12 +5212,12 @@
         <v>71</v>
       </c>
       <c r="E28" s="11" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.45">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="29" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B29" s="10" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C29" s="5">
         <f>C27/2</f>
@@ -5209,20 +5228,20 @@
       </c>
       <c r="E29" s="11"/>
     </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.45">
+    <row r="30" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B30" s="10" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C30" s="5">
         <f>C29*C28/2</f>
         <v>1650</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E30" s="11"/>
     </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.45">
+    <row r="31" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B31" s="10" t="s">
         <v>10</v>
       </c>
@@ -5234,9 +5253,9 @@
       </c>
       <c r="E31" s="11"/>
     </row>
-    <row r="32" spans="2:8" x14ac:dyDescent="0.45">
+    <row r="32" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B32" s="10" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C32" s="5">
         <f>SS303FatigueStrength</f>
@@ -5247,16 +5266,16 @@
       </c>
       <c r="E32" s="11"/>
     </row>
-    <row r="33" spans="2:5" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="33" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B33" s="23" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C33" s="34">
         <f>C30*C31/C32</f>
         <v>9.4827586206896547E-2</v>
       </c>
       <c r="D33" s="34" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E33" s="30"/>
     </row>
@@ -5268,24 +5287,24 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3C7E393-217F-47B1-AEB5-314CED4C9834}">
   <dimension ref="C2:L24"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="4" max="4" width="23.59765625" customWidth="1"/>
+    <col min="4" max="4" width="23.5546875" customWidth="1"/>
     <col min="5" max="5" width="10" customWidth="1"/>
-    <col min="10" max="10" width="29.59765625" customWidth="1"/>
+    <col min="10" max="10" width="29.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="3:12" x14ac:dyDescent="0.45">
+    <row r="2" spans="3:12" x14ac:dyDescent="0.3">
       <c r="J2" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="3" spans="3:12" x14ac:dyDescent="0.45">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="3" spans="3:12" x14ac:dyDescent="0.3">
       <c r="D3" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="4" spans="3:12" x14ac:dyDescent="0.45">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="4" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C4" t="s">
         <v>16</v>
       </c>
@@ -5296,15 +5315,15 @@
         <v>5</v>
       </c>
       <c r="J4" t="s">
+        <v>295</v>
+      </c>
+      <c r="K4" t="s">
         <v>296</v>
       </c>
-      <c r="K4" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="5" spans="3:12" x14ac:dyDescent="0.45">
+    </row>
+    <row r="5" spans="3:12" x14ac:dyDescent="0.3">
       <c r="D5" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="E5">
         <f>AppliedForceNormal/E6</f>
@@ -5315,31 +5334,31 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="K5" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="6" spans="3:12" x14ac:dyDescent="0.45">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="6" spans="3:12" x14ac:dyDescent="0.3">
       <c r="D6" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E6">
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="3:12" x14ac:dyDescent="0.45">
+    <row r="7" spans="3:12" x14ac:dyDescent="0.3">
       <c r="D7" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="E7">
         <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="8" spans="3:12" x14ac:dyDescent="0.45">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="8" spans="3:12" x14ac:dyDescent="0.3">
       <c r="D8" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="E8">
         <v>0.5</v>
@@ -5348,12 +5367,12 @@
         <v>71</v>
       </c>
     </row>
-    <row r="9" spans="3:12" x14ac:dyDescent="0.45">
+    <row r="9" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C9" s="3" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D9" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="E9">
         <v>0.4</v>
@@ -5362,10 +5381,10 @@
         <v>71</v>
       </c>
     </row>
-    <row r="10" spans="3:12" x14ac:dyDescent="0.45">
+    <row r="10" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C10" s="3"/>
       <c r="D10" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="E10">
         <f>(E9+E8)/2</f>
@@ -5375,15 +5394,15 @@
         <v>71</v>
       </c>
       <c r="J10" s="45" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="K10" s="45" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="11" spans="3:12" x14ac:dyDescent="0.45">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="11" spans="3:12" x14ac:dyDescent="0.3">
       <c r="D11" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -5392,7 +5411,7 @@
         <v>71</v>
       </c>
       <c r="J11" s="45" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="K11" s="45">
         <f>'Motor Sizing Calcs'!L8</f>
@@ -5402,21 +5421,21 @@
         <v>103</v>
       </c>
     </row>
-    <row r="12" spans="3:12" x14ac:dyDescent="0.45">
+    <row r="12" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C12" s="3" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D12" t="s">
         <v>116</v>
       </c>
       <c r="E12" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F12" t="s">
         <v>11</v>
       </c>
       <c r="J12" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="K12">
         <v>3.73</v>
@@ -5425,9 +5444,9 @@
         <v>71</v>
       </c>
     </row>
-    <row r="13" spans="3:12" x14ac:dyDescent="0.45">
+    <row r="13" spans="3:12" x14ac:dyDescent="0.3">
       <c r="D13" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="E13">
         <v>18100</v>
@@ -5436,7 +5455,7 @@
         <v>13</v>
       </c>
       <c r="J13" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="K13">
         <f>E10/2</f>
@@ -5446,9 +5465,9 @@
         <v>71</v>
       </c>
     </row>
-    <row r="14" spans="3:12" x14ac:dyDescent="0.45">
+    <row r="14" spans="3:12" x14ac:dyDescent="0.3">
       <c r="D14" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E14">
         <v>27700</v>
@@ -5457,7 +5476,7 @@
         <v>13</v>
       </c>
       <c r="J14" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="K14">
         <f>K12-K13</f>
@@ -5467,18 +5486,18 @@
         <v>71</v>
       </c>
     </row>
-    <row r="15" spans="3:12" x14ac:dyDescent="0.45">
+    <row r="15" spans="3:12" x14ac:dyDescent="0.3">
       <c r="D15" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E15">
         <v>1</v>
       </c>
       <c r="F15" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="J15" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="K15">
         <f>K12+K13</f>
@@ -5488,128 +5507,128 @@
         <v>71</v>
       </c>
     </row>
-    <row r="16" spans="3:12" x14ac:dyDescent="0.45">
+    <row r="16" spans="3:12" x14ac:dyDescent="0.3">
       <c r="D16" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E16">
         <f>E15*J5</f>
         <v>0.33333333333333331</v>
       </c>
       <c r="F16" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="J16" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="K16">
         <f>($K$11*$K$15)</f>
         <v>865.73516370337461</v>
       </c>
       <c r="L16" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="17" spans="4:12" x14ac:dyDescent="0.45">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="17" spans="4:12" x14ac:dyDescent="0.3">
       <c r="D17" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E17">
         <f>E7*E16</f>
         <v>3.333333333333333</v>
       </c>
       <c r="F17" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="J17" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="K17">
         <f>(-1*$K$11*-1*$K$15)</f>
         <v>865.73516370337461</v>
       </c>
       <c r="L17" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="18" spans="4:12" x14ac:dyDescent="0.45">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="18" spans="4:12" x14ac:dyDescent="0.3">
       <c r="J18" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="K18">
         <f>($K$11*-1*$K$14)</f>
         <v>-767.23179488756705</v>
       </c>
       <c r="L18" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="19" spans="4:12" x14ac:dyDescent="0.45">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="19" spans="4:12" x14ac:dyDescent="0.3">
       <c r="D19" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="E19">
         <f>PI()*E8*(E7/2)</f>
         <v>7.8539816339744828</v>
       </c>
       <c r="F19" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="J19" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="K19">
         <f>(-1*$K$11*$K$14)</f>
         <v>-767.23179488756705</v>
       </c>
       <c r="L19" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="20" spans="4:12" x14ac:dyDescent="0.45">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="20" spans="4:12" x14ac:dyDescent="0.3">
       <c r="D20" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="E20">
         <f>((E8/2)^2*PI())-((E9/2)^2*PI())</f>
         <v>7.0685834705770334E-2</v>
       </c>
       <c r="F20" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="K20">
         <f>SUM(K16:K19)</f>
         <v>197.00673763161512</v>
       </c>
       <c r="L20" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="21" spans="4:12" x14ac:dyDescent="0.45">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="21" spans="4:12" x14ac:dyDescent="0.3">
       <c r="K21">
         <f>K20/12</f>
         <v>16.417228135967928</v>
       </c>
       <c r="L21" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="22" spans="4:12" x14ac:dyDescent="0.45">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="22" spans="4:12" x14ac:dyDescent="0.3">
       <c r="D22" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="E22">
         <f>E19*E16</f>
         <v>2.617993877991494</v>
       </c>
     </row>
-    <row r="23" spans="4:12" x14ac:dyDescent="0.45">
+    <row r="23" spans="4:12" x14ac:dyDescent="0.3">
       <c r="E23">
         <f>E5/E22</f>
         <v>114.59155902616466</v>
       </c>
       <c r="J23" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="K23">
         <f>K20/MachineWidth</f>
@@ -5619,13 +5638,13 @@
         <v>4</v>
       </c>
     </row>
-    <row r="24" spans="4:12" x14ac:dyDescent="0.45">
+    <row r="24" spans="4:12" x14ac:dyDescent="0.3">
       <c r="E24">
         <f>E5/E20</f>
         <v>4244.1318157838768</v>
       </c>
       <c r="J24" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="K24">
         <f>K23*MachineHeight/MachineWidth</f>
@@ -5647,156 +5666,164 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FEA2221C-5C0B-46B0-85B0-C1695986BBCC}">
-  <dimension ref="A1:F15"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:F22"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
-    <col min="4" max="4" width="23.3984375" customWidth="1"/>
+    <col min="4" max="4" width="23.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B1" s="45">
+        <v>0.875</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>141</v>
       </c>
-      <c r="B1">
-        <v>0.875</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
-        <v>142</v>
-      </c>
-      <c r="B2">
+      <c r="B2" s="45">
         <v>4</v>
       </c>
       <c r="E2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>142</v>
+      </c>
+      <c r="B3" s="45">
+        <v>21.45</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
         <v>143</v>
       </c>
-      <c r="B3">
-        <v>21.45</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
-        <v>144</v>
-      </c>
-      <c r="B4">
+      <c r="B4" s="57">
         <f>B15</f>
-        <v>7.34</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
+        <v>7.84</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B7" s="5"/>
       <c r="D7" t="s">
+        <v>276</v>
+      </c>
+      <c r="E7" s="56" cm="1">
+        <f t="array" ref="E7">(MMH-PTIH)*(((WCID/2)^2)-((WPRT/2)^2))/((2*((WCID/2)^2))-((WPRT/2)^2))</f>
+        <v>6.6381940970485243</v>
+      </c>
+      <c r="F7" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B8" s="6">
+        <v>2</v>
+      </c>
+      <c r="D8" t="s">
         <v>277</v>
       </c>
-      <c r="E7" cm="1">
-        <f t="array" ref="E7">(MMH-PTIH)*(((WCID/2)^2)-((WPRT/2)^2))/((2*((WCID/2)^2))-((WPRT/2)^2))</f>
-        <v>6.8820660330165087</v>
-      </c>
-      <c r="F7" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A8" s="5" t="s">
+      <c r="E8" s="56">
+        <f>(WPRT^2)*E7/((WCID^2)-(WPRT^2))</f>
+        <v>0.33361180590295147</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" s="5" t="s">
         <v>273</v>
       </c>
-      <c r="B8" s="5">
-        <f>1.5</f>
-        <v>1.5</v>
-      </c>
-      <c r="D8" t="s">
+      <c r="B9" s="6">
+        <v>1.67</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="B10" s="6">
+        <v>1</v>
+      </c>
+      <c r="D10" t="s">
         <v>278</v>
       </c>
-      <c r="E8">
-        <f>(WPRT^2)*E7/((WCID^2)-(WPRT^2))</f>
-        <v>0.34586793396698351</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A9" s="5" t="s">
+      <c r="E10" s="56">
+        <f>E7+E8+B9+B11</f>
+        <v>10.311805902951475</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" s="5" t="s">
         <v>274</v>
       </c>
-      <c r="B9" s="5">
+      <c r="B11" s="6">
         <v>1.67</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A10" s="5" t="s">
-        <v>253</v>
-      </c>
-      <c r="B10" s="5">
+      <c r="D11" t="s">
+        <v>279</v>
+      </c>
+      <c r="E11" s="56">
+        <f>E7+E8+B11</f>
+        <v>8.6418059029514751</v>
+      </c>
+      <c r="F11" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="B12" s="6">
         <v>1</v>
       </c>
-      <c r="D10" t="s">
-        <v>279</v>
-      </c>
-      <c r="E10">
-        <f>E7+E8+B9+B11</f>
-        <v>10.567933966983492</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A11" s="5" t="s">
-        <v>275</v>
-      </c>
-      <c r="B11" s="5">
-        <v>1.67</v>
-      </c>
-      <c r="D11" t="s">
-        <v>280</v>
-      </c>
-      <c r="E11">
-        <f>E7+E8+B11</f>
-        <v>8.8979339669834925</v>
-      </c>
-      <c r="F11" t="s">
+      <c r="D12" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A12" s="5" t="s">
-        <v>252</v>
-      </c>
-      <c r="B12" s="5">
-        <v>1</v>
-      </c>
-      <c r="D12" t="s">
-        <v>282</v>
-      </c>
-      <c r="E12">
+      <c r="E12" s="56">
         <f>E7+E8+B10</f>
-        <v>8.2279339669834926</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
+        <v>7.9718059029514761</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
-        <v>339</v>
-      </c>
-      <c r="B13" s="5">
+        <v>338</v>
+      </c>
+      <c r="B13" s="6">
         <v>0.5</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="5"/>
       <c r="B14" s="5"/>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
-        <v>276</v>
-      </c>
-      <c r="B15" s="5">
+        <v>275</v>
+      </c>
+      <c r="B15" s="55">
         <f>SUM(B8:B13)</f>
-        <v>7.34</v>
+        <v>7.84</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>349</v>
+      </c>
+      <c r="B22" s="56">
+        <f>AppliedForceNormal/(PI()*(WCID/2)^2)</f>
+        <v>47.7464829275686</v>
       </c>
     </row>
   </sheetData>
@@ -5807,103 +5834,103 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCF40096-3C22-48AC-994A-0768CD3A5344}">
   <dimension ref="A5:C19"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.265625" customWidth="1"/>
-    <col min="2" max="2" width="33.59765625" customWidth="1"/>
+    <col min="1" max="1" width="20.21875" customWidth="1"/>
+    <col min="2" max="2" width="33.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
+        <v>224</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
         <v>225</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="B8" t="s">
+        <v>227</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C9" s="3" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C10" s="3" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C11" s="3" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
         <v>209</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A8" t="s">
-        <v>226</v>
-      </c>
-      <c r="B8" t="s">
-        <v>228</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="C9" s="3" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="C10" s="3" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="C11" s="3" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A13" t="s">
+      <c r="B13" t="s">
+        <v>211</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="B13" t="s">
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B14" t="s">
         <v>212</v>
       </c>
-      <c r="C13" s="3" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="B14" t="s">
+      <c r="C14" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="C14" s="3" t="s">
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B15" t="s">
+        <v>215</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="B15" t="s">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B16" t="s">
+        <v>217</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="C15" s="3" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="B16" t="s">
+    </row>
+    <row r="17" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B17" t="s">
+        <v>219</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="C16" s="3" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="17" spans="2:3" x14ac:dyDescent="0.45">
-      <c r="B17" t="s">
+    </row>
+    <row r="18" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B18" t="s">
+        <v>221</v>
+      </c>
+      <c r="C18" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="C17" s="3" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="18" spans="2:3" x14ac:dyDescent="0.45">
-      <c r="B18" t="s">
+    </row>
+    <row r="19" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B19" t="s">
         <v>222</v>
       </c>
-      <c r="C18" s="3" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="19" spans="2:3" x14ac:dyDescent="0.45">
-      <c r="B19" t="s">
+      <c r="C19" s="3" t="s">
         <v>223</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>224</v>
       </c>
     </row>
   </sheetData>
@@ -5928,32 +5955,32 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B5C0A57-75E1-4C82-BEEC-8882CA08F993}">
   <dimension ref="C6:D22"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="95.1328125" customWidth="1"/>
+    <col min="3" max="3" width="95.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="6" spans="3:4" x14ac:dyDescent="0.45">
+    <row r="6" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C6" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="7" spans="3:4" x14ac:dyDescent="0.45">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="7" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C7" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="3:4" x14ac:dyDescent="0.45">
+    <row r="9" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C9" s="2" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="10" spans="3:4" x14ac:dyDescent="0.45">
+    <row r="10" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C10" s="2" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="3:4" x14ac:dyDescent="0.45">
+    <row r="12" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C12" t="s">
         <v>28</v>
       </c>
@@ -5961,7 +5988,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="13" spans="3:4" x14ac:dyDescent="0.45">
+    <row r="13" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C13" t="s">
         <v>30</v>
       </c>
@@ -5969,7 +5996,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="14" spans="3:4" x14ac:dyDescent="0.45">
+    <row r="14" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C14" t="s">
         <v>32</v>
       </c>
@@ -5977,12 +6004,12 @@
         <v>33</v>
       </c>
     </row>
-    <row r="18" spans="3:4" x14ac:dyDescent="0.45">
+    <row r="18" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C18" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="19" spans="3:4" x14ac:dyDescent="0.45">
+    <row r="19" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C19" t="s">
         <v>35</v>
       </c>
@@ -5990,7 +6017,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="20" spans="3:4" x14ac:dyDescent="0.45">
+    <row r="20" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C20" t="s">
         <v>37</v>
       </c>
@@ -5998,7 +6025,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="21" spans="3:4" x14ac:dyDescent="0.45">
+    <row r="21" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C21" t="s">
         <v>39</v>
       </c>
@@ -6006,7 +6033,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="22" spans="3:4" x14ac:dyDescent="0.45">
+    <row r="22" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C22" t="s">
         <v>41</v>
       </c>
